--- a/Rahal_Tour_QA_Testing.xlsx
+++ b/Rahal_Tour_QA_Testing.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB836202-59CC-4EED-A454-F0D13319E9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BBFB038-D359-455E-9B4E-6470642EED23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Summary Report" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="404">
   <si>
     <r>
       <rPr>
@@ -895,9 +895,6 @@
   </si>
   <si>
     <t>Severity</t>
-  </si>
-  <si>
-    <t>Priority</t>
   </si>
   <si>
     <t>Environment</t>
@@ -2014,6 +2011,12 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2034,12 +2037,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2315,17 +2312,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="34.5" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
+      <c r="B1" s="42"/>
       <c r="C1" s="16"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42"/>
+      <c r="B2" s="44"/>
       <c r="C2" s="16"/>
     </row>
     <row r="3" spans="1:3" ht="19.5" customHeight="1">
@@ -2335,16 +2332,16 @@
       <c r="B3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="43"/>
+      <c r="C3" s="45"/>
     </row>
     <row r="4" spans="1:3" ht="19.5" customHeight="1">
       <c r="A4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="43"/>
+      <c r="C4" s="45"/>
     </row>
     <row r="5" spans="1:3" ht="19.5" customHeight="1">
       <c r="A5" s="18" t="s">
@@ -2370,17 +2367,17 @@
       <c r="C7" s="21"/>
     </row>
     <row r="8" spans="1:3" ht="27.75" customHeight="1">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="37"/>
+      <c r="B8" s="39"/>
       <c r="C8" s="21"/>
     </row>
     <row r="9" spans="1:3" ht="99.75" customHeight="1">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="39"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="21"/>
     </row>
     <row r="10" spans="1:3" ht="19.5" customHeight="1">
@@ -2389,10 +2386,10 @@
       <c r="C10" s="21"/>
     </row>
     <row r="11" spans="1:3" ht="28.35" customHeight="1">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="44"/>
+      <c r="B11" s="38"/>
       <c r="C11" s="16"/>
     </row>
     <row r="12" spans="1:3" ht="24" customHeight="1">
@@ -2460,10 +2457,10 @@
       <c r="C19" s="21"/>
     </row>
     <row r="20" spans="1:3" ht="18.75" customHeight="1">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="44"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="21"/>
     </row>
     <row r="21" spans="1:3" ht="31.5" customHeight="1">
@@ -2505,13 +2502,13 @@
     <row r="29" spans="1:3" ht="32.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3759,21 +3756,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" style="3" customWidth="1"/>
     <col min="2" max="2" width="14" style="3" customWidth="1"/>
     <col min="3" max="4" width="32" style="3" customWidth="1"/>
     <col min="5" max="6" width="26" style="3" customWidth="1"/>
-    <col min="7" max="8" width="12" style="3" customWidth="1"/>
-    <col min="9" max="9" width="16" style="3" customWidth="1"/>
-    <col min="10" max="10" width="12" style="3" customWidth="1"/>
-    <col min="11" max="11" width="23" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="8.7109375" style="3"/>
+    <col min="7" max="7" width="12" style="3" customWidth="1"/>
+    <col min="8" max="8" width="16" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12" style="3" customWidth="1"/>
+    <col min="10" max="10" width="23" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5">
+    <row r="1" spans="1:10" ht="28.5">
       <c r="A1" s="1" t="s">
         <v>233</v>
       </c>
@@ -3799,36 +3796,33 @@
         <v>240</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="72">
+      <c r="A2" s="5" t="s">
         <v>242</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="72">
-      <c r="A2" s="5" t="s">
-        <v>243</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>248</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>248</v>
@@ -3839,31 +3833,28 @@
       <c r="J2" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="84">
+      <c r="A3" s="5" t="s">
         <v>251</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="84">
-      <c r="A3" s="5" t="s">
-        <v>252</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>256</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>248</v>
@@ -3872,33 +3863,30 @@
         <v>249</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="K3" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="72">
+      <c r="A4" s="5" t="s">
         <v>257</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="72">
-      <c r="A4" s="5" t="s">
-        <v>258</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="G4" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>248</v>
@@ -3907,33 +3895,30 @@
         <v>249</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="K4" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="60">
+      <c r="A5" s="5" t="s">
         <v>263</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="60">
-      <c r="A5" s="5" t="s">
-        <v>264</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>115</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>268</v>
-      </c>
       <c r="G5" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>248</v>
@@ -3942,33 +3927,30 @@
         <v>249</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="K5" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="48">
+      <c r="A6" s="5" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="48">
-      <c r="A6" s="5" t="s">
-        <v>270</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>121</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>274</v>
-      </c>
       <c r="G6" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>248</v>
@@ -3977,33 +3959,30 @@
         <v>249</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="K6" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60">
+      <c r="A7" s="5" t="s">
         <v>275</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="60">
-      <c r="A7" s="5" t="s">
-        <v>276</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>123</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>280</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>248</v>
@@ -4012,33 +3991,30 @@
         <v>249</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="K7" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="48">
+      <c r="A8" s="5" t="s">
         <v>281</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="48">
-      <c r="A8" s="5" t="s">
-        <v>282</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>141</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>286</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>287</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>248</v>
@@ -4047,33 +4023,30 @@
         <v>249</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="K8" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="60">
+      <c r="A9" s="5" t="s">
         <v>288</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="60">
-      <c r="A9" s="5" t="s">
-        <v>289</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>151</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>293</v>
-      </c>
       <c r="G9" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>248</v>
@@ -4082,33 +4055,30 @@
         <v>249</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="K9" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="84">
+      <c r="A10" s="5" t="s">
         <v>294</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="84">
-      <c r="A10" s="5" t="s">
-        <v>295</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>167</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>299</v>
-      </c>
       <c r="G10" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>248</v>
@@ -4117,13 +4087,10 @@
         <v>249</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -4133,26 +4100,23 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:11">
+    </row>
+    <row r="13" spans="1:10">
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="I15" s="4"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="H15" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4166,7 +4130,7 @@
   <sheetFormatPr defaultColWidth="22.5703125" defaultRowHeight="150.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="40" style="3" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" style="3" customWidth="1"/>
     <col min="3" max="3" width="24.42578125" style="3" customWidth="1"/>
     <col min="4" max="5" width="26.140625" style="3" customWidth="1"/>
     <col min="6" max="7" width="22.5703125" style="3"/>
@@ -4182,13 +4146,13 @@
         <v>29</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>302</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>303</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>237</v>
@@ -4208,22 +4172,22 @@
         <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="H2" s="13" t="s">
         <v>307</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="78" customHeight="1">
@@ -4234,22 +4198,22 @@
         <v>42</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>313</v>
-      </c>
       <c r="H3" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="78" customHeight="1">
@@ -4260,22 +4224,22 @@
         <v>46</v>
       </c>
       <c r="C4" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="F4" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="G4" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="H4" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="120.75" customHeight="1">
@@ -4286,22 +4250,22 @@
         <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>322</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="108" customHeight="1">
@@ -4312,22 +4276,22 @@
         <v>62</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="91.5" customHeight="1">
@@ -4338,22 +4302,22 @@
         <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="H7" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="107.25" customHeight="1">
@@ -4364,22 +4328,22 @@
         <v>90</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="89.25" customHeight="1">
@@ -4390,22 +4354,22 @@
         <v>112</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D9" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="F9" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>335</v>
-      </c>
       <c r="G9" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="89.25" customHeight="1">
@@ -4416,22 +4380,22 @@
         <v>116</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D10" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="F10" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>338</v>
-      </c>
       <c r="G10" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="89.25" customHeight="1">
@@ -4439,25 +4403,25 @@
         <v>121</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="D11" s="13" t="s">
+      <c r="E11" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="F11" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>342</v>
-      </c>
       <c r="G11" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="96.75" customHeight="1">
@@ -4468,22 +4432,22 @@
         <v>124</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D12" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="F12" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="G12" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="G12" s="13" t="s">
-        <v>346</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="101.25" customHeight="1">
@@ -4494,22 +4458,22 @@
         <v>126</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D13" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="F13" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="G13" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="G13" s="13" t="s">
-        <v>350</v>
-      </c>
       <c r="H13" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="111" customHeight="1">
@@ -4520,22 +4484,22 @@
         <v>172</v>
       </c>
       <c r="C14" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="E14" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="F14" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="G14" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>355</v>
-      </c>
       <c r="H14" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="96.75" customHeight="1">
@@ -4546,22 +4510,22 @@
         <v>176</v>
       </c>
       <c r="C15" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="E15" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="F15" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="G15" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>360</v>
-      </c>
       <c r="H15" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="87" customHeight="1">
@@ -4572,22 +4536,22 @@
         <v>138</v>
       </c>
       <c r="C16" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="E16" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="F16" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="G16" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="G16" s="13" t="s">
-        <v>365</v>
-      </c>
       <c r="H16" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="89.25" customHeight="1">
@@ -4598,22 +4562,22 @@
         <v>156</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D17" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="F17" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="G17" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>369</v>
-      </c>
       <c r="H17" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="89.25" customHeight="1">
@@ -4621,25 +4585,25 @@
         <v>141</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="D18" s="13" t="s">
+      <c r="E18" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="F18" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="G18" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="G18" s="13" t="s">
-        <v>374</v>
-      </c>
       <c r="H18" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="89.25" customHeight="1">
@@ -4650,22 +4614,22 @@
         <v>152</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D19" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>376</v>
-      </c>
       <c r="H19" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="101.25" customHeight="1">
@@ -4676,22 +4640,22 @@
         <v>168</v>
       </c>
       <c r="C20" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="E20" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="F20" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="G20" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>381</v>
-      </c>
       <c r="H20" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="93" customHeight="1">
@@ -4702,22 +4666,22 @@
         <v>170</v>
       </c>
       <c r="C21" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="D21" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="E21" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="F21" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="G21" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="G21" s="13" t="s">
-        <v>386</v>
-      </c>
       <c r="H21" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="73.5" customHeight="1">
@@ -4728,22 +4692,22 @@
         <v>180</v>
       </c>
       <c r="C22" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="E22" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="F22" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="F22" s="13" t="s">
+      <c r="G22" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>390</v>
-      </c>
       <c r="H22" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="72" customHeight="1">
@@ -4754,22 +4718,22 @@
         <v>190</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D23" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="F23" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="F23" s="13" t="s">
+      <c r="G23" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>393</v>
-      </c>
       <c r="H23" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="71.25" customHeight="1">
@@ -4780,22 +4744,22 @@
         <v>204</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D24" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="F24" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="E24" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="F24" s="13" t="s">
+      <c r="G24" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="G24" s="13" t="s">
-        <v>396</v>
-      </c>
       <c r="H24" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="75.75" customHeight="1">
@@ -4806,22 +4770,22 @@
         <v>210</v>
       </c>
       <c r="C25" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="E25" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="F25" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="E25" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="F25" s="13" t="s">
+      <c r="G25" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="G25" s="13" t="s">
-        <v>400</v>
-      </c>
       <c r="H25" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="72" customHeight="1">
@@ -4832,22 +4796,22 @@
         <v>232</v>
       </c>
       <c r="C26" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="E26" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="F26" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="F26" s="13" t="s">
+      <c r="G26" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="G26" s="13" t="s">
-        <v>404</v>
-      </c>
       <c r="H26" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
